--- a/output/pdf_financials_xlsx/CLS.xlsx
+++ b/output/pdf_financials_xlsx/CLS.xlsx
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>344</v>
+        <v>268.7</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>367.3</v>
+        <v>243.7</v>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1015.2</v>
+        <v>884.3</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1614.4</v>
+        <v>1462.2</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1921.3</v>
+        <v>1781.3</v>
       </c>
     </row>
     <row r="76">
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>11.1</v>
+        <v>159.2</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>13.5</v>
+        <v>143.2</v>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
@@ -4606,13 +4606,13 @@
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>39.8</v>
+        <v>950.4</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>32.5</v>
+        <v>895.1</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>41.2</v>
+        <v>902.7</v>
       </c>
     </row>
     <row r="86">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">

--- a/output/pdf_financials_xlsx/CLS.xlsx
+++ b/output/pdf_financials_xlsx/CLS.xlsx
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>268.7</v>
+        <v>344</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>243.7</v>
+        <v>367.3</v>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>884.3</v>
+        <v>1015.2</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1462.2</v>
+        <v>1614.4</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1781.3</v>
+        <v>1921.3</v>
       </c>
     </row>
     <row r="76">
@@ -6430,16 +6430,16 @@
         </is>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-33.7</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-48.3</v>
       </c>
     </row>
     <row r="125">
@@ -6476,16 +6476,16 @@
         </is>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-33.7</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-48.3</v>
       </c>
     </row>
     <row r="126">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -21166,7 +21166,11 @@
           <t>Lease payments ................................................................................................... 11</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CLS.xlsx
+++ b/output/pdf_financials_xlsx/CLS.xlsx
@@ -1675,16 +1675,16 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>87</v>
+        <v>15.8</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>77.2</v>
+        <v>13.5</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>81.7</v>
+        <v>11.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>71.7</v>
+        <v>12.2</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>124.7</v>
+        <v>25.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>126.3</v>
+        <v>25.5</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>144.8</v>
+        <v>40.1</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>160.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="29">
@@ -1721,16 +1721,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>206.4</v>
+        <v>135.2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>273.2</v>
+        <v>209.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>193.6</v>
+        <v>123.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>202.4</v>
+        <v>142.9</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>214.9</v>
+        <v>115.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>262.3</v>
+        <v>161.5</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>348.4</v>
+        <v>243.7</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>467</v>
+        <v>346.2</v>
       </c>
     </row>
     <row r="30">
@@ -1767,16 +1767,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.162685217817686</v>
+        <v>2.071681402368949</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.787605711909054</v>
+        <v>2.904478025786774</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.975165970002459</v>
+        <v>1.89328743545611</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.492003243560325</v>
+        <v>2.465450906644123</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.738626676640977</v>
+        <v>2.014578730363076</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.65508367792429</v>
+        <v>2.866168562656397</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.80551724137931</v>
+        <v>3.361379310344828</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.866097223966838</v>
+        <v>4.348699912071348</v>
       </c>
     </row>
     <row r="31">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
